--- a/data/memories/memory_01/locales/es/documents/hr/Employee List Draft.xlsx
+++ b/data/memories/memory_01/locales/es/documents/hr/Employee List Draft.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Employee List Draft</t>
+          <t>Borrador de lista de empleados</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,55 +469,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Draft Employee Directory</t>
+          <t>Borrador del directorio de empleados</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>This document contains the preliminary version of the employee directory prepared for internal review. It has not yet been approved for distribution and may contain incomplete information.</t>
+          <t>Este documento contiene la versión preliminar del directorio de empleados preparado para revisión interna. Aún no ha sido aprobado para su distribución y puede contener información incompleta.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Employee Records</t>
+          <t>Registros de empleados</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Employee ID</t>
+          <t>ID de empleado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Posición</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Estado</t>
         </is>
       </c>
     </row>
@@ -529,22 +529,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sarah K.</t>
+          <t>sara k.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Gestión</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Gerente de Operaciones</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Activo</t>
         </is>
       </c>
     </row>
@@ -561,17 +561,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>Analista financiero</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Activo</t>
         </is>
       </c>
     </row>
@@ -583,22 +583,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Laura L.</t>
+          <t>laura l.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Recursos humanos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HR Specialist</t>
+          <t>Especialista en Recursos Humanos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Activo</t>
         </is>
       </c>
     </row>
@@ -610,22 +610,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Oliver M.</t>
+          <t>óliver m.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>Instalaciones</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Facilities Coordinator</t>
+          <t>Coordinador de Instalaciones</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Activo</t>
         </is>
       </c>
     </row>
@@ -642,17 +642,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ÉL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Administrador de sistemas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Activo</t>
         </is>
       </c>
     </row>
@@ -664,102 +664,102 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M. R.</t>
+          <t>SEÑOR.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Operaciones</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Project Coordinator</t>
+          <t>Coordinador de Proyectos</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Review Required</t>
+          <t>Revisión requerida</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Review Notes</t>
+          <t>Notas de revisión</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>• Verify employee identifiers against historical registry.</t>
+          <t>• Verifique los identificadores de los empleados con el registro histórico.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>• Confirm department assignments after organisation update.</t>
+          <t>• Confirme las asignaciones de departamento después de la actualización de la organización.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>• Review incomplete personnel documentation.</t>
+          <t>• Revisar documentación de personal incompleta.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>• Do not publish until approval is received.</t>
+          <t>• No publicar hasta recibir la aprobación.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Outstanding Questions</t>
+          <t>Preguntas pendientes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>One record requires additional verification because the current department assignment does not match the previous organisational documentation.</t>
+          <t>Un registro requiere verificación adicional porque la asignación de departamento actual no coincide con la documentación organizacional anterior.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>The employee identifier remains valid, but supporting information could not be confirmed during the first review.</t>
+          <t>El identificador del empleado sigue siendo válido, pero la información de respaldo no pudo confirmarse durante la primera revisión.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Revision History</t>
+          <t>Historial de revisiones</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Version</t>
+          <t>Versión</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Change</t>
+          <t>Cambiar</t>
         </is>
       </c>
     </row>
@@ -771,12 +771,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>05 Sep</t>
+          <t>05 sep</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Initial compilation</t>
+          <t>Compilación inicial</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>08 Sep</t>
+          <t>08 sep</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Updated departments</t>
+          <t>Departamentos actualizados</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12 Sep</t>
+          <t>12 de septiembre</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Added review comments</t>
+          <t>Comentarios de revisión agregados</t>
         </is>
       </c>
     </row>
